--- a/sesc_musica_capital_2026_07.xlsx
+++ b/sesc_musica_capital_2026_07.xlsx
@@ -515,7 +515,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Extraído em: 06/07/2026 20:25   |   Fonte: PDF Em Cartaz – sescsp.org.br</t>
+          <t>Extraído em: 25/07/2026 13:14   |   Fonte: PDF Em Cartaz – sescsp.org.br</t>
         </is>
       </c>
     </row>

--- a/sesc_musica_capital_2026_07.xlsx
+++ b/sesc_musica_capital_2026_07.xlsx
@@ -515,7 +515,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Extraído em: 25/07/2026 13:14   |   Fonte: PDF Em Cartaz – sescsp.org.br</t>
+          <t>Extraído em: 28/07/2026 14:37   |   Fonte: PDF Em Cartaz – sescsp.org.br</t>
         </is>
       </c>
     </row>
